--- a/link_budget/RF_phase1.xlsx
+++ b/link_budget/RF_phase1.xlsx
@@ -1,16 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/fl1023_ic_ac_uk/Documents/Year 3/GDP/GDP/link_budget/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="166" documentId="11_E564EA96B5990B6BCCAB59E2B46B37C5AED9A70F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6760EFF-8015-4FCA-94E2-18E6323778C4}"/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13540"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="model1" sheetId="3" r:id="rId1"/>
-    <sheet name="uplink" sheetId="4" r:id="rId2"/>
-    <sheet name="relay" sheetId="5" r:id="rId3"/>
-    <sheet name="phase1" sheetId="6" r:id="rId4"/>
+    <sheet name="CSS" sheetId="7" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId3"/>
+    <sheet name="uplink" sheetId="4" r:id="rId4"/>
+    <sheet name="relay" sheetId="5" r:id="rId5"/>
+    <sheet name="phase1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="224">
   <si>
     <t>Category</t>
   </si>
@@ -438,24 +446,407 @@
   </si>
   <si>
     <t>L3</t>
+  </si>
+  <si>
+    <t>Star topology</t>
+  </si>
+  <si>
+    <t>System / Architecture Type</t>
+  </si>
+  <si>
+    <t>Basic Structure</t>
+  </si>
+  <si>
+    <t>Typical Use in Space Missions</t>
+  </si>
+  <si>
+    <t>Advantages</t>
+  </si>
+  <si>
+    <t>Disadvantages</t>
+  </si>
+  <si>
+    <t>Point-to-point / Direct link</t>
+  </si>
+  <si>
+    <t>Basic Earth–spacecraft TT&amp;C link; direct telemetry downlink and command uplink</t>
+  </si>
+  <si>
+    <t>Simple architecture; easiest to model with link budget; fewer routing complications</t>
+  </si>
+  <si>
+    <t>Operationally simple; no dependency on relay node; good for crew safety</t>
+  </si>
+  <si>
+    <t>Lander needs larger antenna or higher power; lunar terrain/attitude may limit visibility</t>
+  </si>
+  <si>
+    <t>Relay architecture</t>
+  </si>
+  <si>
+    <t>Mars rover–orbiter–Earth links; lunar relay satellites; surface assets with limited power</t>
+  </si>
+  <si>
+    <t>Relay becomes a critical node; adds routing, timing, and reliability complexity</t>
+  </si>
+  <si>
+    <t>Multi-spacecraft missions with a mothership and deployable elements</t>
+  </si>
+  <si>
+    <t>Easier than full mesh; centralised control; simpler network management</t>
+  </si>
+  <si>
+    <t>Hub failure affects many links; hub needs high reliability and redundancy</t>
+  </si>
+  <si>
+    <t>Very suitable. The transfer vehicle can act as communication hub between Earth, lander, and return capsule</t>
+  </si>
+  <si>
+    <t>Mesh topology</t>
+  </si>
+  <si>
+    <t>Distributed satellite networks; resilient constellations; military/robust networks</t>
+  </si>
+  <si>
+    <t>High redundancy; multiple fallback paths; improves fault tolerance</t>
+  </si>
+  <si>
+    <t>Complex routing; more radios/antennas; higher power, mass, software complexity</t>
+  </si>
+  <si>
+    <t>Probably too complex as a baseline, but useful as a comparison option in literature review</t>
+  </si>
+  <si>
+    <t>Hybrid topology</t>
+  </si>
+  <si>
+    <t>Combination of DTE, relay, star, and backup links</t>
+  </si>
+  <si>
+    <t>Most realistic spacecraft TT&amp;C systems</t>
+  </si>
+  <si>
+    <t>Balances robustness and practicality; supports nominal and emergency modes</t>
+  </si>
+  <si>
+    <t>More complex than pure DTE; needs careful interface definition</t>
+  </si>
+  <si>
+    <t>Best recommendation for your mission: DTE for safety, relay for high-rate/coverage, low-rate backup for emergency</t>
+  </si>
+  <si>
+    <t>Store-and-forward</t>
+  </si>
+  <si>
+    <t>Data is stored onboard and transmitted later when link conditions are favourable</t>
+  </si>
+  <si>
+    <t>Science data return, delayed telemetry, non-real-time payload data</t>
+  </si>
+  <si>
+    <t>Reduces need for continuous high-rate link; allows data return during scheduled windows</t>
+  </si>
+  <si>
+    <t>Not suitable for real-time crew safety; requires onboard storage</t>
+  </si>
+  <si>
+    <t>Very relevant for 72-hour surface stay. Video/science/housekeeping logs can be stored and transmitted during scheduled passes</t>
+  </si>
+  <si>
+    <t>Real-time continuous link</t>
+  </si>
+  <si>
+    <t>Communication maintained continuously or near-continuously</t>
+  </si>
+  <si>
+    <t>Crewed mission voice, biomedical telemetry, emergency monitoring</t>
+  </si>
+  <si>
+    <t>Best for safety and mission control awareness</t>
+  </si>
+  <si>
+    <t>Expensive in link capacity and ground coverage; may require multiple ground stations or relay</t>
+  </si>
+  <si>
+    <t>Needed for crew voice, emergency telemetry, and critical command links, but not necessarily for all data</t>
+  </si>
+  <si>
+    <t>Ground-station network link</t>
+  </si>
+  <si>
+    <t>Spacecraft communicates with multiple possible Earth ground stations</t>
+  </si>
+  <si>
+    <t>DSN, ESTRACK, commercial ground networks</t>
+  </si>
+  <si>
+    <t>Increases visibility time; improves operational flexibility</t>
+  </si>
+  <si>
+    <t>Scheduling constraints; network access may be limited</t>
+  </si>
+  <si>
+    <t>You need this under “ground system selection.” For lunar distance, several ground networks are possible</t>
+  </si>
+  <si>
+    <t>Redundant TT&amp;C chain</t>
+  </si>
+  <si>
+    <t>Duplicate transponders, amplifiers, antennas, switches, or cross-strapped RF chains</t>
+  </si>
+  <si>
+    <t>High-reliability spacecraft, deep-space missions, crewed systems</t>
+  </si>
+  <si>
+    <t>Improves probability of mission success; protects against single-point failures</t>
+  </si>
+  <si>
+    <t>Adds mass, power, complexity, and integration effort</t>
+  </si>
+  <si>
+    <t>Very important because your mission target is &gt;99.9% success probability</t>
+  </si>
+  <si>
+    <t>Adaptive data-rate / modulation system</t>
+  </si>
+  <si>
+    <t>Modulation, coding, or data rate changes depending on link quality</t>
+  </si>
+  <si>
+    <t>Modern space links, Ka-band/high-rate links, variable geometry missions</t>
+  </si>
+  <si>
+    <t>Better throughput when link is good; safer operation when link is poor</t>
+  </si>
+  <si>
+    <t>More complex; requires careful verification</t>
+  </si>
+  <si>
+    <t>Useful as an advanced option. Literature says link margin depends on SNR variation and coding behaviour, not just a fixed 3 dB rule</t>
+  </si>
+  <si>
+    <t>Optical communication</t>
+  </si>
+  <si>
+    <t>Laser communication instead of RF</t>
+  </si>
+  <si>
+    <t>Future high-rate deep-space and lunar communications</t>
+  </si>
+  <si>
+    <t>Very high data rate; smaller beam divergence; potentially lower antenna mass</t>
+  </si>
+  <si>
+    <t>Requires very accurate pointing; weather/cloud sensitivity for ground stations; less mature than RF</t>
+  </si>
+  <si>
+    <t>Good to mention as future/alternative architecture, but RF is safer for baseline crewed TTC</t>
+  </si>
+  <si>
+    <t>Relevance to the mission</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> lander communicates directly with Earth without relay</t>
+  </si>
+  <si>
+    <t>Demo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apollo-style lunar communication; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>emergency communications</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>direct command uplink</t>
+    </r>
+  </si>
+  <si>
+    <t>LTV ↔ Lander, Lander ↔ Capsule, Capsule ↔ LTV, plus Earth links</t>
+  </si>
+  <si>
+    <r>
+      <t>Requires each spacecraft to have enough</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> antenna gain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>transmit power</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Earth visibility</t>
+    </r>
+  </si>
+  <si>
+    <t>Essential baseline for the mission</t>
+  </si>
+  <si>
+    <t>Very important for crewed safety. Even if high-rate data uses relay, a low-rate DTE emergency channel is strongly recommended; when emergency mode is activated direct link is used</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reduces surface vehicle power/antenna burden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; can improve coverage; useful when lander cannot point well at Earth</t>
+    </r>
+  </si>
+  <si>
+    <t>Strong candidate for the mission; The lunar transfer vehicle or a lunar-orbit asset could relay lander telemetry/video</t>
+  </si>
+  <si>
+    <t>Earth ⇄ Lunar Lander
+Earth ⇄ Lunar Transfer Vehicle
+Earth ⇄ Return Capsule</t>
+  </si>
+  <si>
+    <t>Lunar Lander ⇄ Lunar Transfer Vehicle ⇄ Earth</t>
+  </si>
+  <si>
+    <t>The lander sends data to the transfer vehicle first. The transfer vehicle then forwards it to Earth. Commands can also go from Earth to the transfer vehicle, then to the lander.</t>
+  </si>
+  <si>
+    <t>One central node acts as the communication hub. Other vehicles communicate mainly through this hub.</t>
+  </si>
+  <si>
+    <t>Earth ⇄ Lunar Transfer Vehicle ⇄ Lunar Lander , Return Capsule ,Surface Systems</t>
+  </si>
+  <si>
+    <t>Multiple nodes communicate with each other directly.</t>
+  </si>
+  <si>
+    <t>Earth ⇅ ┌────────────┼────────────┐ ⇅ ⇅ ⇅ LTV ⇄────── Lander ⇄──── Return Capsule ⇅ ⇅ Backup Surface crew/system link</t>
+  </si>
+  <si>
+    <t>Lander records data → Onboard storage → Wait for link window → Earth</t>
+  </si>
+  <si>
+    <t>Crew / Lander ⇄ Earth Mission Control continuous voice / telemetry / command</t>
+  </si>
+  <si>
+    <t>spacecraft takl to multiple ground station at the same time</t>
+  </si>
+  <si>
+    <t>Spacecraft laser terminal ───── optical beam ─────&gt; Optical ground station</t>
+  </si>
+  <si>
+    <t>Increase/decrease the antenna gain&amp;change of frequency at the relay</t>
+  </si>
+  <si>
+    <t>The system changes data rate or margin during the mission</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -474,151 +865,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -627,37 +888,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,115 +930,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -789,72 +942,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -942,259 +1047,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -1209,16 +1069,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
@@ -1230,19 +1084,19 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
@@ -1251,10 +1105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
@@ -1263,90 +1114,204 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1357,7 +1322,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1385,157 +1350,47 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1782,71 +1637,66 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="7.421875" customWidth="1"/>
-    <col min="3" max="3" width="26.6875" customWidth="1"/>
-    <col min="4" max="4" width="24.8671875" customWidth="1"/>
-    <col min="5" max="5" width="17.578125" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
-    <col min="7" max="7" width="56.125" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="56.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="20"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
-      <c r="A3" s="15" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="21"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
@@ -1859,17 +1709,17 @@
         <v>12</v>
       </c>
       <c r="E4">
-        <v>40.4314</v>
+        <v>40.431399999999996</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
@@ -1887,12 +1737,12 @@
       <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
@@ -1910,18 +1760,18 @@
       <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="18" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
@@ -1934,17 +1784,17 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>40.4314</v>
+        <v>40.431399999999996</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
@@ -1962,12 +1812,12 @@
       <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -1985,12 +1835,12 @@
       <c r="F10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
@@ -2008,18 +1858,18 @@
       <c r="F11" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B13" t="s">
@@ -2037,12 +1887,12 @@
       <c r="F13" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B14" t="s">
@@ -2060,12 +1910,12 @@
       <c r="F14" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="18" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B15" t="s">
@@ -2078,17 +1928,17 @@
         <v>56</v>
       </c>
       <c r="E15">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="F15" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B16" t="s">
@@ -2106,12 +1956,12 @@
       <c r="F16" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="18" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B17" t="s">
@@ -2129,12 +1979,12 @@
       <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="18" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B18" t="s">
@@ -2152,12 +2002,12 @@
       <c r="F18" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="18" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B19" t="s">
@@ -2175,12 +2025,12 @@
       <c r="F19" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B20" t="s">
@@ -2198,18 +2048,18 @@
       <c r="F20" t="s">
         <v>62</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="18" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="22"/>
+      <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B22" t="s">
@@ -2227,12 +2077,12 @@
       <c r="F22" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B23" t="s">
@@ -2250,12 +2100,12 @@
       <c r="F23" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B24" t="s">
@@ -2273,12 +2123,12 @@
       <c r="F24" t="s">
         <v>92</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B25" t="s">
@@ -2296,12 +2146,12 @@
       <c r="F25" t="s">
         <v>62</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="G25" s="18" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B26" t="s">
@@ -2319,18 +2169,18 @@
       <c r="F26" t="s">
         <v>101</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="18" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="22"/>
+      <c r="G27" s="18"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B28" t="s">
@@ -2348,12 +2198,12 @@
       <c r="F28" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="22" t="s">
+      <c r="G28" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B29" t="s">
@@ -2371,12 +2221,12 @@
       <c r="F29" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="18" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B30" t="s">
@@ -2394,12 +2244,12 @@
       <c r="F30" t="s">
         <v>62</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="18" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B31" t="s">
@@ -2417,80 +2267,75 @@
       <c r="F31" t="s">
         <v>62</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="18" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32" s="23" t="s">
+      <c r="F32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="19" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="20"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="17"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="21"/>
+      <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B36" t="s">
@@ -2503,17 +2348,17 @@
         <v>12</v>
       </c>
       <c r="E36">
-        <v>40.4314</v>
+        <v>40.431399999999996</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B37" t="s">
@@ -2531,12 +2376,12 @@
       <c r="F37" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="G37" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B38" t="s">
@@ -2554,18 +2399,18 @@
       <c r="F38" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="18" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G39" s="22"/>
+      <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B40" t="s">
@@ -2578,17 +2423,17 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>40.4314</v>
+        <v>40.431399999999996</v>
       </c>
       <c r="F40" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B41" t="s">
@@ -2606,12 +2451,12 @@
       <c r="F41" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B42" t="s">
@@ -2629,12 +2474,12 @@
       <c r="F42" t="s">
         <v>36</v>
       </c>
-      <c r="G42" s="22" t="s">
+      <c r="G42" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B43" t="s">
@@ -2652,18 +2497,18 @@
       <c r="F43" t="s">
         <v>13</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G44" s="22"/>
+      <c r="G44" s="18"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B45" t="s">
@@ -2681,12 +2526,12 @@
       <c r="F45" t="s">
         <v>47</v>
       </c>
-      <c r="G45" s="22" t="s">
+      <c r="G45" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B46" t="s">
@@ -2704,12 +2549,12 @@
       <c r="F46" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="22" t="s">
+      <c r="G46" s="18" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B47" t="s">
@@ -2722,17 +2567,17 @@
         <v>56</v>
       </c>
       <c r="E47">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="F47" t="s">
         <v>57</v>
       </c>
-      <c r="G47" s="22" t="s">
+      <c r="G47" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B48" t="s">
@@ -2750,12 +2595,12 @@
       <c r="F48" t="s">
         <v>62</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="18" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B49" t="s">
@@ -2773,12 +2618,12 @@
       <c r="F49" t="s">
         <v>13</v>
       </c>
-      <c r="G49" s="22" t="s">
+      <c r="G49" s="18" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B50" t="s">
@@ -2796,12 +2641,12 @@
       <c r="F50" t="s">
         <v>62</v>
       </c>
-      <c r="G50" s="22" t="s">
+      <c r="G50" s="18" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B51" t="s">
@@ -2819,12 +2664,12 @@
       <c r="F51" t="s">
         <v>62</v>
       </c>
-      <c r="G51" s="22" t="s">
+      <c r="G51" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B52" t="s">
@@ -2842,18 +2687,18 @@
       <c r="F52" t="s">
         <v>62</v>
       </c>
-      <c r="G52" s="22" t="s">
+      <c r="G52" s="18" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G53" s="22"/>
+      <c r="G53" s="18"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B54" t="s">
@@ -2871,12 +2716,12 @@
       <c r="F54" t="s">
         <v>62</v>
       </c>
-      <c r="G54" s="22" t="s">
+      <c r="G54" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B55" t="s">
@@ -2894,12 +2739,12 @@
       <c r="F55" t="s">
         <v>62</v>
       </c>
-      <c r="G55" s="22" t="s">
+      <c r="G55" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B56" t="s">
@@ -2917,12 +2762,12 @@
       <c r="F56" t="s">
         <v>92</v>
       </c>
-      <c r="G56" s="22" t="s">
+      <c r="G56" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B57" t="s">
@@ -2940,12 +2785,12 @@
       <c r="F57" t="s">
         <v>62</v>
       </c>
-      <c r="G57" s="22" t="s">
+      <c r="G57" s="18" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B58" t="s">
@@ -2963,18 +2808,18 @@
       <c r="F58" t="s">
         <v>101</v>
       </c>
-      <c r="G58" s="22" t="s">
+      <c r="G58" s="18" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G59" s="22"/>
+      <c r="G59" s="18"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B60" t="s">
@@ -2992,12 +2837,12 @@
       <c r="F60" t="s">
         <v>62</v>
       </c>
-      <c r="G60" s="22" t="s">
+      <c r="G60" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B61" t="s">
@@ -3015,12 +2860,12 @@
       <c r="F61" t="s">
         <v>111</v>
       </c>
-      <c r="G61" s="22" t="s">
+      <c r="G61" s="18" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B62" t="s">
@@ -3038,12 +2883,12 @@
       <c r="F62" t="s">
         <v>62</v>
       </c>
-      <c r="G62" s="22" t="s">
+      <c r="G62" s="18" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B63" t="s">
@@ -3061,80 +2906,75 @@
       <c r="F63" t="s">
         <v>62</v>
       </c>
-      <c r="G63" s="22" t="s">
+      <c r="G63" s="18" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G64" s="23" t="s">
+      <c r="F64" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G64" s="19" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G65" s="12" t="s">
+      <c r="G65" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="20"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="17"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="21"/>
+      <c r="G67" s="18"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B68" t="s">
@@ -3152,12 +2992,12 @@
       <c r="F68" t="s">
         <v>13</v>
       </c>
-      <c r="G68" s="22" t="s">
+      <c r="G68" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B69" t="s">
@@ -3175,12 +3015,12 @@
       <c r="F69" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="22" t="s">
+      <c r="G69" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B70" t="s">
@@ -3198,18 +3038,18 @@
       <c r="F70" t="s">
         <v>22</v>
       </c>
-      <c r="G70" s="22" t="s">
+      <c r="G70" s="18" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G71" s="22"/>
+      <c r="G71" s="18"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B72" t="s">
@@ -3227,12 +3067,12 @@
       <c r="F72" t="s">
         <v>47</v>
       </c>
-      <c r="G72" s="22" t="s">
+      <c r="G72" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B73" t="s">
@@ -3250,12 +3090,12 @@
       <c r="F73" t="s">
         <v>52</v>
       </c>
-      <c r="G73" s="22" t="s">
+      <c r="G73" s="18" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B74" t="s">
@@ -3273,12 +3113,12 @@
       <c r="F74" t="s">
         <v>57</v>
       </c>
-      <c r="G74" s="22" t="s">
+      <c r="G74" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B75" t="s">
@@ -3296,12 +3136,12 @@
       <c r="F75" t="s">
         <v>62</v>
       </c>
-      <c r="G75" s="22" t="s">
+      <c r="G75" s="18" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B76" t="s">
@@ -3319,12 +3159,12 @@
       <c r="F76" t="s">
         <v>13</v>
       </c>
-      <c r="G76" s="22" t="s">
+      <c r="G76" s="18" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B77" t="s">
@@ -3342,12 +3182,12 @@
       <c r="F77" t="s">
         <v>62</v>
       </c>
-      <c r="G77" s="22" t="s">
+      <c r="G77" s="18" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B78" t="s">
@@ -3365,12 +3205,12 @@
       <c r="F78" t="s">
         <v>62</v>
       </c>
-      <c r="G78" s="22" t="s">
+      <c r="G78" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B79" t="s">
@@ -3388,18 +3228,18 @@
       <c r="F79" t="s">
         <v>62</v>
       </c>
-      <c r="G79" s="22" t="s">
+      <c r="G79" s="18" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="15" t="s">
+      <c r="A80" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G80" s="22"/>
+      <c r="G80" s="18"/>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B81" t="s">
@@ -3417,12 +3257,12 @@
       <c r="F81" t="s">
         <v>62</v>
       </c>
-      <c r="G81" s="22" t="s">
+      <c r="G81" s="18" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B82" t="s">
@@ -3440,12 +3280,12 @@
       <c r="F82" t="s">
         <v>62</v>
       </c>
-      <c r="G82" s="22" t="s">
+      <c r="G82" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B83" t="s">
@@ -3463,13 +3303,13 @@
       <c r="F83" t="s">
         <v>92</v>
       </c>
-      <c r="G83" s="22">
+      <c r="G83" s="18">
         <f>10^(E83/10)</f>
         <v>31.6227766016838</v>
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B84" t="s">
@@ -3487,12 +3327,12 @@
       <c r="F84" t="s">
         <v>62</v>
       </c>
-      <c r="G84" s="22" t="s">
+      <c r="G84" s="18" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B85" t="s">
@@ -3510,23 +3350,18 @@
       <c r="F85" t="s">
         <v>101</v>
       </c>
-      <c r="G85" s="22" t="s">
+      <c r="G85" s="18" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="21"/>
+      <c r="G86" s="18"/>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
@@ -3544,12 +3379,12 @@
       <c r="F87" t="s">
         <v>13</v>
       </c>
-      <c r="G87" s="22" t="s">
+      <c r="G87" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="16" t="s">
+      <c r="A88" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B88" t="s">
@@ -3567,12 +3402,12 @@
       <c r="F88" t="s">
         <v>13</v>
       </c>
-      <c r="G88" s="22" t="s">
+      <c r="G88" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B89" t="s">
@@ -3590,18 +3425,18 @@
       <c r="F89" t="s">
         <v>22</v>
       </c>
-      <c r="G89" s="22" t="s">
+      <c r="G89" s="18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="90" customFormat="1" spans="1:7">
-      <c r="A90" s="17" t="s">
+    <row r="90" spans="1:7">
+      <c r="A90" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G90" s="22"/>
+      <c r="G90" s="18"/>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B91" t="s">
@@ -3619,12 +3454,12 @@
       <c r="F91" t="s">
         <v>62</v>
       </c>
-      <c r="G91" s="22" t="s">
+      <c r="G91" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B92" t="s">
@@ -3642,12 +3477,12 @@
       <c r="F92" t="s">
         <v>111</v>
       </c>
-      <c r="G92" s="22" t="s">
+      <c r="G92" s="18" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B93" t="s">
@@ -3665,12 +3500,12 @@
       <c r="F93" t="s">
         <v>62</v>
       </c>
-      <c r="G93" s="22" t="s">
+      <c r="G93" s="18" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="16" t="s">
+      <c r="A94" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B94" t="s">
@@ -3688,1444 +3523,1701 @@
       <c r="F94" t="s">
         <v>62</v>
       </c>
-      <c r="G94" s="22" t="s">
+      <c r="G94" s="18" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="18" t="s">
+      <c r="A95" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B95" s="19" t="s">
+      <c r="B95" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C95" s="19" t="s">
+      <c r="C95" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D95" s="19" t="s">
+      <c r="D95" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="E95" s="19" t="s">
+      <c r="E95" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="F95" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G95" s="23" t="s">
+      <c r="F95" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G95" s="19" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:7">
-      <c r="A96" s="16"/>
-      <c r="B96"/>
-      <c r="C96"/>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96" s="22"/>
+      <c r="A96" s="13"/>
+      <c r="G96" s="18"/>
     </row>
     <row r="97" spans="1:7">
-      <c r="A97" s="16"/>
-      <c r="B97"/>
-      <c r="C97"/>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97" s="22"/>
+      <c r="A97" s="13"/>
+      <c r="G97" s="18"/>
     </row>
     <row r="98" spans="1:7">
-      <c r="A98" s="16"/>
-      <c r="B98"/>
-      <c r="C98"/>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
-      <c r="G98" s="22"/>
-    </row>
-    <row r="99" customFormat="1" spans="1:7">
-      <c r="A99" s="15"/>
-      <c r="G99" s="22"/>
+      <c r="A98" s="13"/>
+      <c r="G98" s="18"/>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="12"/>
+      <c r="G99" s="18"/>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="16"/>
-      <c r="B100"/>
-      <c r="C100"/>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
-      <c r="G100" s="22"/>
+      <c r="A100" s="13"/>
+      <c r="G100" s="18"/>
     </row>
     <row r="101" spans="1:7">
-      <c r="A101" s="16"/>
-      <c r="B101"/>
-      <c r="C101"/>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101" s="22"/>
+      <c r="A101" s="13"/>
+      <c r="G101" s="18"/>
     </row>
     <row r="102" spans="1:7">
-      <c r="A102" s="16"/>
-      <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102" s="22"/>
+      <c r="A102" s="13"/>
+      <c r="G102" s="18"/>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="16"/>
-      <c r="B103"/>
-      <c r="C103"/>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103" s="22"/>
+      <c r="A103" s="13"/>
+      <c r="G103" s="18"/>
     </row>
     <row r="104" spans="1:7">
-      <c r="A104" s="16"/>
-      <c r="B104"/>
-      <c r="C104"/>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104" s="22"/>
+      <c r="A104" s="13"/>
+      <c r="G104" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629CED2D-83A7-45B9-A445-34823B141F27}">
+  <dimension ref="A1:T13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="7.421875" customWidth="1"/>
-    <col min="3" max="3" width="26.6875" customWidth="1"/>
-    <col min="4" max="4" width="24.8671875" customWidth="1"/>
-    <col min="5" max="5" width="17.578125" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
-    <col min="7" max="7" width="56.125" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" style="20" customWidth="1"/>
+    <col min="3" max="3" width="33" style="20" customWidth="1"/>
+    <col min="4" max="4" width="35.5546875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="34.5546875" style="20" customWidth="1"/>
+    <col min="7" max="7" width="41.21875" style="20" customWidth="1"/>
+    <col min="8" max="8" width="22.77734375" style="20" customWidth="1"/>
+    <col min="9" max="20" width="8.88671875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
-      <c r="A3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>384400</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>17.43</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>78.35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17">
-        <v>45</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E24">
-        <v>17</v>
-      </c>
-      <c r="F24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26">
-        <v>25</v>
-      </c>
-      <c r="F26" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29">
-        <v>15</v>
-      </c>
-      <c r="F29" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" t="s">
-        <v>119</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
-        <v>121</v>
-      </c>
-      <c r="B32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32" t="s">
-        <v>125</v>
+    <row r="1" spans="1:7" ht="28.8">
+      <c r="A1" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="52.2" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="59.4" customHeight="1">
+      <c r="A3" s="31"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="72.599999999999994" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="96" customHeight="1">
+      <c r="A5" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="65.400000000000006" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="56.4" customHeight="1">
+      <c r="A7" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60.6" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="58.2" customHeight="1">
+      <c r="A9" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="58.2" customHeight="1">
+      <c r="A10" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="68.400000000000006" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="70.8" customHeight="1">
+      <c r="A12" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="63.6" customHeight="1">
+      <c r="A13" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="7.421875" customWidth="1"/>
-    <col min="3" max="3" width="26.6875" customWidth="1"/>
-    <col min="4" max="4" width="24.8671875" customWidth="1"/>
-    <col min="5" max="5" width="17.578125" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
-    <col min="7" max="7" width="56.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
-      <c r="A3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>384400</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8">
-        <v>17.43</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>78.35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17">
-        <v>45</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E24">
-        <v>17</v>
-      </c>
-      <c r="F24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26">
-        <v>25</v>
-      </c>
-      <c r="F26" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29">
-        <v>15</v>
-      </c>
-      <c r="F29" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" t="s">
-        <v>119</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
-        <v>121</v>
-      </c>
-      <c r="B32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32" t="s">
-        <v>125</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3476FCC-427C-4C31-BBAD-0C6794473B06}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="56.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>384400</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>17.43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>78.349999999999994</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="F29" t="s">
+        <v>111</v>
+      </c>
+      <c r="G29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="56.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>384400</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>17.43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>78.349999999999994</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="F29" t="s">
+        <v>111</v>
+      </c>
+      <c r="G29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>